--- a/Topic_Date_Tracker.xlsx
+++ b/Topic_Date_Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daily_Challenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C24EE7E-0EFB-4737-B3A5-39D044F9FD08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7632EFED-C5D1-48FC-BC70-EE7B6BF0FAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Topics</t>
   </si>
@@ -40,6 +40,21 @@
   </si>
   <si>
     <t>No. Of Questions</t>
+  </si>
+  <si>
+    <t>GRAPG BFS DFS (Islands, Surrounded Islands)</t>
+  </si>
+  <si>
+    <t>SQL/Simple DP/Binary_Tree_Vertical_and_Pruning</t>
+  </si>
+  <si>
+    <t>JAOff</t>
+  </si>
+  <si>
+    <t>Stack, Design , Two Pointer</t>
+  </si>
+  <si>
+    <t>DP, PQ, SLDNG, LRC ,DL,</t>
   </si>
 </sst>
 </file>
@@ -75,8 +90,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -357,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="74.6640625" customWidth="1"/>
@@ -365,7 +382,7 @@
     <col min="3" max="3" width="38.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -375,8 +392,11 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -385,6 +405,59 @@
       </c>
       <c r="C2" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>45567</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2">
+        <v>45573</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2">
+        <v>45575</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>45578</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
